--- a/gamePrices.xlsx
+++ b/gamePrices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,17 +436,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Metroid</t>
+          <t>Aether</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.ebgames.ca/Switch2</t>
+          <t>https://store.steampowered.com/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Error reaching site</t>
+          <t>$ 39.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aether &amp; Iron</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://store.steampowered.com/</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>$ 39.99</t>
         </is>
       </c>
     </row>

--- a/gamePrices.xlsx
+++ b/gamePrices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,24 +446,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$ 39.99</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Aether &amp; Iron</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://store.steampowered.com/</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>$ 39.99</t>
+          <t>$ 25.99</t>
         </is>
       </c>
     </row>

--- a/gamePrices.xlsx
+++ b/gamePrices.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aether</t>
+          <t>Meat</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -446,7 +446,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$ 25.99</t>
+          <t>$ 39.99</t>
         </is>
       </c>
     </row>

--- a/gamePrices.xlsx
+++ b/gamePrices.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Meat</t>
+          <t>I am Jesus Christ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -446,7 +446,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$ 39.99</t>
+          <t>No price found</t>
         </is>
       </c>
     </row>
